--- a/artfynd/A 30154-2022 artfynd.xlsx
+++ b/artfynd/A 30154-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30154-2022 artfynd.xlsx
+++ b/artfynd/A 30154-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83823717</v>
+        <v>89103920</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,25 +705,33 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3459, 30006077, Upl</t>
+          <t>Siggesta, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>700611.681532281</v>
+        <v>700606</v>
       </c>
       <c r="R2" t="n">
-        <v>6586453.549526823</v>
+        <v>6586467</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,317 +753,43 @@
           <t>Värmdö</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>92FB3642-C151-45D5-A196-27DFD7448ACB</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-06-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-06-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Enstaka individer på mossbeklädd ekstam.</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Miguel Jaramillo</t>
+          <t>Elin Gawell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Miguel Jaramillo</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>83823600</v>
-      </c>
-      <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>3459, 30006078, Upl</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>700621.2888354999</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6586465.293873571</v>
-      </c>
-      <c r="S3" t="n">
-        <v>25</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Värmdö</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Värmdö</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>566ECFFC-0E95-4D69-9C15-A40124C0D322</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2009-06-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2009-06-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Miguel Jaramillo</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Miguel Jaramillo</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>89103920</v>
-      </c>
-      <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Siggesta, Upl</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>700605.877596928</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6586466.51825179</v>
-      </c>
-      <c r="S4" t="n">
-        <v>50</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Värmdö</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Värmdö</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2020-11-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2020-11-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Enstaka individer på mossbeklädd ekstam.</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
           <t>Elin Gawell</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Elin Gawell</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30154-2022 artfynd.xlsx
+++ b/artfynd/A 30154-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,8 +795,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89103920</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>